--- a/catalog_products_2026-03-30 00_00_31.xlsx
+++ b/catalog_products_2026-03-30 00_00_31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="125">
   <si>
     <t># Required | A unique content ID for the item. Use the item's SKU if you can. Each content ID must appear only once in your catalog. To run dynamic ads this ID must exactly match the content ID for the same item in your Meta Pixel code. Character limit: 100</t>
   </si>
@@ -413,10 +413,10 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF12824D"/>
-      <name val="Courier New"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -454,17 +454,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
@@ -1286,7 +1288,7 @@
       <c r="F3" t="s">
         <v>84</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>85</v>
       </c>
       <c r="H3" t="s">
@@ -1431,6 +1433,117 @@
       </c>
       <c r="I4" t="s">
         <v>124</v>
+      </c>
+      <c r="J4" t="s">
+        <v>88</v>
+      </c>
+      <c r="K4" t="s">
+        <v>89</v>
+      </c>
+      <c r="L4" t="s">
+        <v>90</v>
+      </c>
+      <c r="M4" t="s">
+        <v>84</v>
+      </c>
+      <c r="N4" t="s">
+        <v>91</v>
+      </c>
+      <c r="P4" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>93</v>
+      </c>
+      <c r="R4" t="s">
+        <v>94</v>
+      </c>
+      <c r="S4" t="s">
+        <v>95</v>
+      </c>
+      <c r="T4" t="s">
+        <v>96</v>
+      </c>
+      <c r="U4" t="s">
+        <v>97</v>
+      </c>
+      <c r="V4" t="s">
+        <v>98</v>
+      </c>
+      <c r="W4" t="s">
+        <v>99</v>
+      </c>
+      <c r="X4" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>111</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1527,7 +1640,12 @@
       <formula1>1000</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1"/>
+    <hyperlink ref="H4" r:id="rId2"/>
+    <hyperlink ref="G4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>